--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -5090,7 +5090,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251030_201456.xlsx
@@ -4274,7 +4274,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
